--- a/media/templates/preinvoice_template.xlsx
+++ b/media/templates/preinvoice_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Desktop\CRM_FLOW\media\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dorsa-Co\Desktop\GitlabRepoes\Seketala_Kitchen_Flow\media\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3999B5-231B-473F-9AA9-0CF975861F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D203058-7DEB-482D-84C7-99C940679D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,9 +36,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
-    <t>شماره پیش‌فاکتور:</t>
-  </si>
-  <si>
     <t>____</t>
   </si>
   <si>
@@ -66,9 +63,6 @@
     <t>ردیف</t>
   </si>
   <si>
-    <t>نوع سنگ</t>
-  </si>
-  <si>
     <t>ابعاد</t>
   </si>
   <si>
@@ -96,16 +90,22 @@
     <t>مبلغ نهایی قابل پرداخت:</t>
   </si>
   <si>
-    <t>امضا و مهر کارخانه</t>
-  </si>
-  <si>
-    <t>پیش فاکتور</t>
-  </si>
-  <si>
-    <t>کارخانه سنگ‌بری K.B.C</t>
-  </si>
-  <si>
-    <t>آدرس: شهرک صنعتی، خیابان صنعت 5 - تلفن: 031345678920</t>
+    <t>شماره فاکتور:</t>
+  </si>
+  <si>
+    <t>محصول</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> مهر شرکت</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> فاکتور فروش</t>
+  </si>
+  <si>
+    <t>مرکز تهیه و توزیع کالا دیجیتال آریارایان</t>
+  </si>
+  <si>
+    <t>آدرس: خیابان احمدآباد ، کوچه 32 ، مرکز تهیه و توزیع کالا دیجیتال آریارایان</t>
   </si>
 </sst>
 </file>
@@ -165,7 +165,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -539,6 +539,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
@@ -547,30 +571,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -881,7 +881,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="55.85546875" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
@@ -890,26 +890,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="33"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="41"/>
     </row>
     <row r="2" spans="1:7" ht="21">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="36"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="33"/>
     </row>
     <row r="3" spans="1:7" ht="22.5">
       <c r="A3" s="28" t="s">
@@ -924,72 +924,72 @@
     </row>
     <row r="4" spans="1:7" ht="23.25" customHeight="1">
       <c r="A4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="17" t="s">
+      <c r="G4" s="16" t="s">
         <v>2</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="17" t="s">
-        <v>6</v>
-      </c>
       <c r="G5" s="16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="38"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="35"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="G7" s="10" t="s">
         <v>13</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1064,7 +1064,7 @@
       <c r="D15" s="20"/>
       <c r="E15" s="21"/>
       <c r="F15" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G15" s="4">
         <f>SUM(G9:G14)</f>
@@ -1078,10 +1078,10 @@
       <c r="D16" s="23"/>
       <c r="E16" s="24"/>
       <c r="F16" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" thickBot="1">
@@ -1091,7 +1091,7 @@
       <c r="D17" s="26"/>
       <c r="E17" s="27"/>
       <c r="F17" s="13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
         <f>G15-G16</f>
